--- a/评奖评优/甲团/20260527/计研五三2025—2026学年清华大学研究生甲级团支部汇总表.xlsx
+++ b/评奖评优/甲团/20260527/计研五三2025—2026学年清华大学研究生甲级团支部汇总表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12780"/>
+    <workbookView windowWidth="28260" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,747 +80,7 @@
     <t>否</t>
   </si>
   <si>
-    <r>
-      <t>计研五三支部是计算机系纵向研究生基层集体</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>班级</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>36</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>人、团员</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>30</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>人、党员</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>20</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>博士比例</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>74.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。支部以</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>党建引领、育人为本、党团班一体化发展</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>为主线</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>:2024</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年构建</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>实践</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>—</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>理论</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>—</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>党课</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>—</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>交流</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"PTCF</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>思政模型</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完成</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>85</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>项重点工作</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>获评第七期班团养成计划</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>笃行班团</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>";2025</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年深化</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以人为本</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>五育并举</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>品牌</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全年开展</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>14</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>次组织生活、党性修养</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>次、五育并举活动</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>15</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>次</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>完成</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>173</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>项党团班工作</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>校系平台发推文</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>18</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>篇</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>联学共建从系内拓展至社科院系、社区与政府</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>牵头</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>数实融合新引擎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>智创产业新未来</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>雁行实践并参与清华大学雁行主视频拍摄</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>笃行班团</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>晋升</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>卓越班团</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>"(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全校前五</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
+    <t>计研五三支部是清华大学计算机系纵向研究生基层集体，班级36人，博士占比74.5%，现有团员30人、党员20人。支部坚持以"党建引领、育人为本、党团班一体化发展"为主线。2024年，支部构建"实践—理论—党课—交流"PTCF四位一体思政模型，全年完成85项重点工作，获评第七期班团养成计划"笃行班团"。2025年，支部深化"以人为本·五育并举"品牌建设，全年开展组织生活14次、党性修养专题学习11次、五育并举活动15次，累计完成党团班工作173项，在校系平台发布推文18篇；联学共建从系内拓展至社科院系、社区及政府部门，牵头"数实融合新引擎·智创产业新未来"雁行实践并参与清华大学雁行主视频拍摄，成功从"笃行班团"跃升为"卓越班团"（全校前五）。</t>
   </si>
 </sst>
 </file>
@@ -862,6 +122,13 @@
     </font>
     <font>
       <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="仿宋"/>
@@ -878,13 +145,6 @@
       <b/>
       <sz val="14"/>
       <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1492,34 +752,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1991,92 +1251,92 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
     </row>
-    <row r="2" ht="26" customHeight="1" spans="1:1">
-      <c r="A2" s="4" t="s">
+    <row r="2" ht="26" customHeight="1" spans="1:22">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="41" customHeight="1" spans="1:11">
-      <c r="A3" s="5" t="s">
+    <row r="3" ht="41" customHeight="1" spans="1:22">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="143" customHeight="1" spans="1:16">
-      <c r="A4" s="7">
+    <row r="4" s="1" customFormat="1" ht="143" customHeight="1" spans="1:22">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="9">
         <v>36</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="9">
         <v>30</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="9">
         <v>20</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <v>0</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="11">
         <v>0</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
     </row>
     <row r="29" ht="16.8" customHeight="1"/>
   </sheetData>
